--- a/Quant_SmallCap/Quant_SmallCap_Equity_Analysis.xlsx
+++ b/Quant_SmallCap/Quant_SmallCap_Equity_Analysis.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG191"/>
+  <dimension ref="A1:AJ198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -500,6 +500,9 @@
     <col width="15" customWidth="1" min="31" max="31"/>
     <col width="15" customWidth="1" min="32" max="32"/>
     <col width="15" customWidth="1" min="33" max="33"/>
+    <col width="15" customWidth="1" min="34" max="34"/>
+    <col width="15" customWidth="1" min="35" max="35"/>
+    <col width="15" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,6 +578,11 @@
           <t>November 2025</t>
         </is>
       </c>
+      <c r="AH2" s="3" t="inlineStr">
+        <is>
+          <t>December 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="D3" s="2" t="inlineStr">
@@ -727,6 +735,21 @@
           <t>% Net Assets</t>
         </is>
       </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>Market Value (Rs. Lakhs)</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>% Net Assets</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -834,6 +857,15 @@
       <c r="AG4" s="8" t="n">
         <v>0.10160455</v>
       </c>
+      <c r="AH4" s="6" t="n">
+        <v>18567876</v>
+      </c>
+      <c r="AI4" s="7" t="n">
+        <v>291589.92</v>
+      </c>
+      <c r="AJ4" s="8" t="n">
+        <v>0.09789971</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -941,6 +973,15 @@
       <c r="AG5" s="8" t="n">
         <v>0.06139252</v>
       </c>
+      <c r="AH5" s="6" t="n">
+        <v>60489693</v>
+      </c>
+      <c r="AI5" s="7" t="n">
+        <v>178414.35</v>
+      </c>
+      <c r="AJ5" s="8" t="n">
+        <v>0.05990163</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1048,6 +1089,15 @@
       <c r="AG6" s="8" t="n">
         <v>0.03925428</v>
       </c>
+      <c r="AH6" s="6" t="n">
+        <v>37909419</v>
+      </c>
+      <c r="AI6" s="7" t="n">
+        <v>119717.95</v>
+      </c>
+      <c r="AJ6" s="8" t="n">
+        <v>0.04019464</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1155,6 +1205,15 @@
       <c r="AG7" s="8" t="n">
         <v>0.03337132</v>
       </c>
+      <c r="AH7" s="6" t="n">
+        <v>13184087</v>
+      </c>
+      <c r="AI7" s="7" t="n">
+        <v>94609.00999999999</v>
+      </c>
+      <c r="AJ7" s="8" t="n">
+        <v>0.03176445</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1262,6 +1321,15 @@
       <c r="AG8" s="8" t="n">
         <v>0.02954255</v>
       </c>
+      <c r="AH8" s="6" t="n">
+        <v>60430545</v>
+      </c>
+      <c r="AI8" s="7" t="n">
+        <v>86409.64</v>
+      </c>
+      <c r="AJ8" s="8" t="n">
+        <v>0.02901156</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1369,6 +1437,15 @@
       <c r="AG9" s="8" t="n">
         <v>0.02466001</v>
       </c>
+      <c r="AH9" s="6" t="n">
+        <v>2575324</v>
+      </c>
+      <c r="AI9" s="7" t="n">
+        <v>80154.38</v>
+      </c>
+      <c r="AJ9" s="8" t="n">
+        <v>0.02691139</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1476,6 +1553,15 @@
       <c r="AG10" s="8" t="n">
         <v>0.02493567</v>
       </c>
+      <c r="AH10" s="6" t="n">
+        <v>11305160</v>
+      </c>
+      <c r="AI10" s="7" t="n">
+        <v>69735.88</v>
+      </c>
+      <c r="AJ10" s="8" t="n">
+        <v>0.02341344</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1583,6 +1669,15 @@
       <c r="AG11" s="8" t="n">
         <v>0.02180428</v>
       </c>
+      <c r="AH11" s="6" t="n">
+        <v>9172820</v>
+      </c>
+      <c r="AI11" s="7" t="n">
+        <v>68777.8</v>
+      </c>
+      <c r="AJ11" s="8" t="n">
+        <v>0.02309177</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1690,6 +1785,15 @@
       <c r="AG12" s="8" t="n">
         <v>0.02179082</v>
       </c>
+      <c r="AH12" s="6" t="n">
+        <v>3457016</v>
+      </c>
+      <c r="AI12" s="7" t="n">
+        <v>61317.09</v>
+      </c>
+      <c r="AJ12" s="8" t="n">
+        <v>0.02058688</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1797,6 +1901,15 @@
       <c r="AG13" s="8" t="n">
         <v>0.02011701</v>
       </c>
+      <c r="AH13" s="6" t="n">
+        <v>8398925</v>
+      </c>
+      <c r="AI13" s="7" t="n">
+        <v>64075.4</v>
+      </c>
+      <c r="AJ13" s="8" t="n">
+        <v>0.02151296</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1904,6 +2017,15 @@
       <c r="AG14" s="8" t="n">
         <v>0.01865513</v>
       </c>
+      <c r="AH14" s="6" t="n">
+        <v>2468292</v>
+      </c>
+      <c r="AI14" s="7" t="n">
+        <v>55282.34</v>
+      </c>
+      <c r="AJ14" s="8" t="n">
+        <v>0.01856074</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2011,6 +2133,15 @@
       <c r="AG15" s="8" t="n">
         <v>0.02108147</v>
       </c>
+      <c r="AH15" s="6" t="n">
+        <v>14661224</v>
+      </c>
+      <c r="AI15" s="7" t="n">
+        <v>86142.02</v>
+      </c>
+      <c r="AJ15" s="8" t="n">
+        <v>0.02892171</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2118,6 +2249,15 @@
       <c r="AG16" s="8" t="n">
         <v>0.01774204</v>
       </c>
+      <c r="AH16" s="6" t="n">
+        <v>28625736</v>
+      </c>
+      <c r="AI16" s="7" t="n">
+        <v>52339.3</v>
+      </c>
+      <c r="AJ16" s="8" t="n">
+        <v>0.01757263</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2225,6 +2365,15 @@
       <c r="AG17" s="8" t="n">
         <v>0.01862096</v>
       </c>
+      <c r="AH17" s="6" t="n">
+        <v>89972615</v>
+      </c>
+      <c r="AI17" s="7" t="n">
+        <v>60992.44</v>
+      </c>
+      <c r="AJ17" s="8" t="n">
+        <v>0.02047787</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2332,6 +2481,15 @@
       <c r="AG18" s="8" t="n">
         <v>0.01895408</v>
       </c>
+      <c r="AH18" s="6" t="n">
+        <v>49004963</v>
+      </c>
+      <c r="AI18" s="7" t="n">
+        <v>59673.34</v>
+      </c>
+      <c r="AJ18" s="8" t="n">
+        <v>0.020035</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2439,6 +2597,15 @@
       <c r="AG19" s="8" t="n">
         <v>0.01519876</v>
       </c>
+      <c r="AH19" s="6" t="n">
+        <v>10716104</v>
+      </c>
+      <c r="AI19" s="7" t="n">
+        <v>48651.11</v>
+      </c>
+      <c r="AJ19" s="8" t="n">
+        <v>0.01633434</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2546,6 +2713,15 @@
       <c r="AG20" s="8" t="n">
         <v>0.02225576</v>
       </c>
+      <c r="AH20" s="6" t="n">
+        <v>4335570</v>
+      </c>
+      <c r="AI20" s="7" t="n">
+        <v>71233.42</v>
+      </c>
+      <c r="AJ20" s="8" t="n">
+        <v>0.02391623</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -2653,6 +2829,15 @@
       <c r="AG21" s="8" t="n">
         <v>0.01666675</v>
       </c>
+      <c r="AH21" s="6" t="n">
+        <v>22502050</v>
+      </c>
+      <c r="AI21" s="7" t="n">
+        <v>46925.78</v>
+      </c>
+      <c r="AJ21" s="8" t="n">
+        <v>0.01575507</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2760,6 +2945,15 @@
       <c r="AG22" s="8" t="n">
         <v>0.01601522</v>
       </c>
+      <c r="AH22" s="6" t="n">
+        <v>1037211</v>
+      </c>
+      <c r="AI22" s="7" t="n">
+        <v>47276.08</v>
+      </c>
+      <c r="AJ22" s="8" t="n">
+        <v>0.01587268</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -2867,6 +3061,15 @@
       <c r="AG23" s="8" t="n">
         <v>0.01482511</v>
       </c>
+      <c r="AH23" s="6" t="n">
+        <v>499707</v>
+      </c>
+      <c r="AI23" s="7" t="n">
+        <v>1201.2</v>
+      </c>
+      <c r="AJ23" s="8" t="n">
+        <v>0.0004032899999999999</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2974,6 +3177,15 @@
       <c r="AG24" s="8" t="n">
         <v>0.0150806</v>
       </c>
+      <c r="AH24" s="6" t="n">
+        <v>914527</v>
+      </c>
+      <c r="AI24" s="7" t="n">
+        <v>45613.86</v>
+      </c>
+      <c r="AJ24" s="8" t="n">
+        <v>0.0153146</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3081,6 +3293,15 @@
       <c r="AG25" s="8" t="n">
         <v>0.01729905</v>
       </c>
+      <c r="AH25" s="6" t="n">
+        <v>14805881</v>
+      </c>
+      <c r="AI25" s="7" t="n">
+        <v>46942.05</v>
+      </c>
+      <c r="AJ25" s="8" t="n">
+        <v>0.01576053</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3188,6 +3409,15 @@
       <c r="AG26" s="8" t="n">
         <v>0.01288915</v>
       </c>
+      <c r="AH26" s="6" t="n">
+        <v>9033845</v>
+      </c>
+      <c r="AI26" s="7" t="n">
+        <v>41067.86</v>
+      </c>
+      <c r="AJ26" s="8" t="n">
+        <v>0.01378831</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3295,6 +3525,15 @@
       <c r="AG27" s="8" t="n">
         <v>0.01568841</v>
       </c>
+      <c r="AH27" s="6" t="n">
+        <v>39945165</v>
+      </c>
+      <c r="AI27" s="7" t="n">
+        <v>50962.04</v>
+      </c>
+      <c r="AJ27" s="8" t="n">
+        <v>0.01711022</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3402,6 +3641,15 @@
       <c r="AG28" s="8" t="n">
         <v>0.01226112</v>
       </c>
+      <c r="AH28" s="6" t="n">
+        <v>4319413</v>
+      </c>
+      <c r="AI28" s="7" t="n">
+        <v>35177.3</v>
+      </c>
+      <c r="AJ28" s="8" t="n">
+        <v>0.01181058</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -3509,6 +3757,15 @@
       <c r="AG29" s="8" t="n">
         <v>0.01407111</v>
       </c>
+      <c r="AH29" s="6" t="n">
+        <v>7303592</v>
+      </c>
+      <c r="AI29" s="7" t="n">
+        <v>41929.92</v>
+      </c>
+      <c r="AJ29" s="8" t="n">
+        <v>0.01407774</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3616,6 +3873,15 @@
       <c r="AG30" s="8" t="n">
         <v>0.01169717</v>
       </c>
+      <c r="AH30" s="6" t="n">
+        <v>6712318</v>
+      </c>
+      <c r="AI30" s="7" t="n">
+        <v>34910.77</v>
+      </c>
+      <c r="AJ30" s="8" t="n">
+        <v>0.0117211</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -3723,6 +3989,15 @@
       <c r="AG31" s="8" t="n">
         <v>0.01114892</v>
       </c>
+      <c r="AH31" s="6" t="n">
+        <v>6219091</v>
+      </c>
+      <c r="AI31" s="7" t="n">
+        <v>32755.95</v>
+      </c>
+      <c r="AJ31" s="8" t="n">
+        <v>0.01099763</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -3830,6 +4105,15 @@
       <c r="AG32" s="8" t="n">
         <v>0.00983209</v>
       </c>
+      <c r="AH32" s="6" t="n">
+        <v>17305369</v>
+      </c>
+      <c r="AI32" s="7" t="n">
+        <v>27764.73</v>
+      </c>
+      <c r="AJ32" s="8" t="n">
+        <v>0.00932186</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3937,6 +4221,15 @@
       <c r="AG33" s="8" t="n">
         <v>0.01160837</v>
       </c>
+      <c r="AH33" s="6" t="n">
+        <v>6479838</v>
+      </c>
+      <c r="AI33" s="7" t="n">
+        <v>36031.14</v>
+      </c>
+      <c r="AJ33" s="8" t="n">
+        <v>0.01209726</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -4044,6 +4337,15 @@
       <c r="AG34" s="8" t="n">
         <v>0.01064494</v>
       </c>
+      <c r="AH34" s="6" t="n">
+        <v>2947185</v>
+      </c>
+      <c r="AI34" s="7" t="n">
+        <v>31632.14</v>
+      </c>
+      <c r="AJ34" s="8" t="n">
+        <v>0.01062032</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -4151,6 +4453,15 @@
       <c r="AG35" s="8" t="n">
         <v>0.00972723</v>
       </c>
+      <c r="AH35" s="6" t="n">
+        <v>3555936</v>
+      </c>
+      <c r="AI35" s="7" t="n">
+        <v>32015.87</v>
+      </c>
+      <c r="AJ35" s="8" t="n">
+        <v>0.01074915</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4258,6 +4569,15 @@
       <c r="AG36" s="8" t="n">
         <v>0.00889553</v>
       </c>
+      <c r="AH36" s="6" t="n">
+        <v>6641314</v>
+      </c>
+      <c r="AI36" s="7" t="n">
+        <v>25695.24</v>
+      </c>
+      <c r="AJ36" s="8" t="n">
+        <v>0.008627040000000001</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -4365,6 +4685,15 @@
       <c r="AG37" s="8" t="n">
         <v>0.009354919999999999</v>
       </c>
+      <c r="AH37" s="6" t="n">
+        <v>2737754</v>
+      </c>
+      <c r="AI37" s="7" t="n">
+        <v>28327.54</v>
+      </c>
+      <c r="AJ37" s="8" t="n">
+        <v>0.00951082</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -4472,6 +4801,15 @@
       <c r="AG38" s="8" t="n">
         <v>0.009208330000000001</v>
       </c>
+      <c r="AH38" s="6" t="n">
+        <v>3767715</v>
+      </c>
+      <c r="AI38" s="7" t="n">
+        <v>27327.24</v>
+      </c>
+      <c r="AJ38" s="8" t="n">
+        <v>0.009174969999999999</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -4579,6 +4917,15 @@
       <c r="AG39" s="8" t="n">
         <v>0.008052460000000001</v>
       </c>
+      <c r="AH39" s="6" t="n">
+        <v>16714161</v>
+      </c>
+      <c r="AI39" s="7" t="n">
+        <v>25087.96</v>
+      </c>
+      <c r="AJ39" s="8" t="n">
+        <v>0.008423140000000001</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -4686,6 +5033,15 @@
       <c r="AG40" s="8" t="n">
         <v>0.00802693</v>
       </c>
+      <c r="AH40" s="6" t="n">
+        <v>1376279</v>
+      </c>
+      <c r="AI40" s="7" t="n">
+        <v>23699.52</v>
+      </c>
+      <c r="AJ40" s="8" t="n">
+        <v>0.007956980000000001</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -4793,6 +5149,15 @@
       <c r="AG41" s="8" t="n">
         <v>0.01037423</v>
       </c>
+      <c r="AH41" s="6" t="n">
+        <v>14754512</v>
+      </c>
+      <c r="AI41" s="7" t="n">
+        <v>30320.52</v>
+      </c>
+      <c r="AJ41" s="8" t="n">
+        <v>0.01017995</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -4900,6 +5265,15 @@
       <c r="AG42" s="8" t="n">
         <v>0.00774801</v>
       </c>
+      <c r="AH42" s="6" t="n">
+        <v>3682926</v>
+      </c>
+      <c r="AI42" s="7" t="n">
+        <v>23994.26</v>
+      </c>
+      <c r="AJ42" s="8" t="n">
+        <v>0.008055940000000001</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5007,6 +5381,15 @@
       <c r="AG43" s="8" t="n">
         <v>0.009571939999999999</v>
       </c>
+      <c r="AH43" s="6" t="n">
+        <v>3465947</v>
+      </c>
+      <c r="AI43" s="7" t="n">
+        <v>26304.8</v>
+      </c>
+      <c r="AJ43" s="8" t="n">
+        <v>0.00883169</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -5114,6 +5497,15 @@
       <c r="AG44" s="8" t="n">
         <v>0.008765490000000001</v>
       </c>
+      <c r="AH44" s="6" t="n">
+        <v>26531392</v>
+      </c>
+      <c r="AI44" s="7" t="n">
+        <v>31821.75</v>
+      </c>
+      <c r="AJ44" s="8" t="n">
+        <v>0.01068398</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5221,6 +5613,15 @@
       <c r="AG45" s="8" t="n">
         <v>0.005277960000000001</v>
       </c>
+      <c r="AH45" s="6" t="n">
+        <v>875658</v>
+      </c>
+      <c r="AI45" s="7" t="n">
+        <v>8257.450000000001</v>
+      </c>
+      <c r="AJ45" s="8" t="n">
+        <v>0.00277239</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -5328,6 +5729,15 @@
       <c r="AG46" s="8" t="n">
         <v>0.00476679</v>
       </c>
+      <c r="AH46" s="6" t="n">
+        <v>5979730</v>
+      </c>
+      <c r="AI46" s="7" t="n">
+        <v>15210.64</v>
+      </c>
+      <c r="AJ46" s="8" t="n">
+        <v>0.005106889999999999</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -5435,6 +5845,15 @@
       <c r="AG47" s="8" t="n">
         <v>0.00486209</v>
       </c>
+      <c r="AH47" s="6" t="n">
+        <v>10610336</v>
+      </c>
+      <c r="AI47" s="7" t="n">
+        <v>14223.16</v>
+      </c>
+      <c r="AJ47" s="8" t="n">
+        <v>0.00477535</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -5542,6 +5961,15 @@
       <c r="AG48" s="8" t="n">
         <v>0.00534283</v>
       </c>
+      <c r="AH48" s="6" t="n">
+        <v>7899233</v>
+      </c>
+      <c r="AI48" s="7" t="n">
+        <v>16999.94</v>
+      </c>
+      <c r="AJ48" s="8" t="n">
+        <v>0.005707640000000001</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5649,6 +6077,15 @@
       <c r="AG49" s="8" t="n">
         <v>0.00587969</v>
       </c>
+      <c r="AH49" s="6" t="n">
+        <v>377551</v>
+      </c>
+      <c r="AI49" s="7" t="n">
+        <v>15884.7</v>
+      </c>
+      <c r="AJ49" s="8" t="n">
+        <v>0.0053332</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -5756,6 +6193,15 @@
       <c r="AG50" s="8" t="n">
         <v>0.0059794</v>
       </c>
+      <c r="AH50" s="6" t="n">
+        <v>12121807</v>
+      </c>
+      <c r="AI50" s="7" t="n">
+        <v>15827.44</v>
+      </c>
+      <c r="AJ50" s="8" t="n">
+        <v>0.00531398</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -5863,6 +6309,15 @@
       <c r="AG51" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -5970,6 +6425,15 @@
       <c r="AG52" s="8" t="n">
         <v>0.00468393</v>
       </c>
+      <c r="AH52" s="6" t="n">
+        <v>18082269</v>
+      </c>
+      <c r="AI52" s="7" t="n">
+        <v>13883.57</v>
+      </c>
+      <c r="AJ52" s="8" t="n">
+        <v>0.00466133</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6077,6 +6541,15 @@
       <c r="AG53" s="8" t="n">
         <v>0.00468403</v>
       </c>
+      <c r="AH53" s="6" t="n">
+        <v>7662294</v>
+      </c>
+      <c r="AI53" s="7" t="n">
+        <v>13986.75</v>
+      </c>
+      <c r="AJ53" s="8" t="n">
+        <v>0.00469597</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -6184,6 +6657,15 @@
       <c r="AG54" s="8" t="n">
         <v>0.00470802</v>
       </c>
+      <c r="AH54" s="6" t="n">
+        <v>1315790</v>
+      </c>
+      <c r="AI54" s="7" t="n">
+        <v>12400</v>
+      </c>
+      <c r="AJ54" s="8" t="n">
+        <v>0.00416323</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6291,6 +6773,15 @@
       <c r="AG55" s="8" t="n">
         <v>0.004607780000000001</v>
       </c>
+      <c r="AH55" s="6" t="n">
+        <v>4174238</v>
+      </c>
+      <c r="AI55" s="7" t="n">
+        <v>15607.48</v>
+      </c>
+      <c r="AJ55" s="8" t="n">
+        <v>0.00524012</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -6398,6 +6889,15 @@
       <c r="AG56" s="8" t="n">
         <v>0.00356527</v>
       </c>
+      <c r="AH56" s="6" t="n">
+        <v>4199230</v>
+      </c>
+      <c r="AI56" s="7" t="n">
+        <v>9851.389999999999</v>
+      </c>
+      <c r="AJ56" s="8" t="n">
+        <v>0.00330755</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -6505,6 +7005,15 @@
       <c r="AG57" s="8" t="n">
         <v>0.00337598</v>
       </c>
+      <c r="AH57" s="6" t="n">
+        <v>3649318</v>
+      </c>
+      <c r="AI57" s="7" t="n">
+        <v>10185.25</v>
+      </c>
+      <c r="AJ57" s="8" t="n">
+        <v>0.00341964</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -6612,6 +7121,15 @@
       <c r="AG58" s="8" t="n">
         <v>0.00519865</v>
       </c>
+      <c r="AH58" s="6" t="n">
+        <v>1745594</v>
+      </c>
+      <c r="AI58" s="7" t="n">
+        <v>16000.11</v>
+      </c>
+      <c r="AJ58" s="8" t="n">
+        <v>0.005371949999999999</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -6719,6 +7237,15 @@
       <c r="AG59" s="8" t="n">
         <v>0.00267826</v>
       </c>
+      <c r="AH59" s="6" t="n">
+        <v>1465799</v>
+      </c>
+      <c r="AI59" s="7" t="n">
+        <v>7726.23</v>
+      </c>
+      <c r="AJ59" s="8" t="n">
+        <v>0.00259404</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6826,6 +7353,15 @@
       <c r="AG60" s="8" t="n">
         <v>0.00324855</v>
       </c>
+      <c r="AH60" s="6" t="n">
+        <v>4193748</v>
+      </c>
+      <c r="AI60" s="7" t="n">
+        <v>9103.370000000001</v>
+      </c>
+      <c r="AJ60" s="8" t="n">
+        <v>0.00305641</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -6933,6 +7469,15 @@
       <c r="AG61" s="8" t="n">
         <v>0.00268254</v>
       </c>
+      <c r="AH61" s="6" t="n">
+        <v>4701490</v>
+      </c>
+      <c r="AI61" s="7" t="n">
+        <v>7817.17</v>
+      </c>
+      <c r="AJ61" s="8" t="n">
+        <v>0.00262457</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7040,6 +7585,15 @@
       <c r="AG62" s="8" t="n">
         <v>0.00297851</v>
       </c>
+      <c r="AH62" s="6" t="n">
+        <v>2730499</v>
+      </c>
+      <c r="AI62" s="7" t="n">
+        <v>8596.98</v>
+      </c>
+      <c r="AJ62" s="8" t="n">
+        <v>0.00288639</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7147,6 +7701,15 @@
       <c r="AG63" s="8" t="n">
         <v>0.00256213</v>
       </c>
+      <c r="AH63" s="6" t="n">
+        <v>6030000</v>
+      </c>
+      <c r="AI63" s="7" t="n">
+        <v>7711.16</v>
+      </c>
+      <c r="AJ63" s="8" t="n">
+        <v>0.00258898</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -7254,6 +7817,15 @@
       <c r="AG64" s="8" t="n">
         <v>0.00237899</v>
       </c>
+      <c r="AH64" s="6" t="n">
+        <v>815006</v>
+      </c>
+      <c r="AI64" s="7" t="n">
+        <v>6551.43</v>
+      </c>
+      <c r="AJ64" s="8" t="n">
+        <v>0.00219961</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7361,6 +7933,15 @@
       <c r="AG65" s="8" t="n">
         <v>0.00281973</v>
       </c>
+      <c r="AH65" s="6" t="n">
+        <v>1900591</v>
+      </c>
+      <c r="AI65" s="7" t="n">
+        <v>8446.23</v>
+      </c>
+      <c r="AJ65" s="8" t="n">
+        <v>0.00283577</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -7468,6 +8049,15 @@
       <c r="AG66" s="8" t="n">
         <v>0.00267958</v>
       </c>
+      <c r="AH66" s="6" t="n">
+        <v>1897034</v>
+      </c>
+      <c r="AI66" s="7" t="n">
+        <v>7573.91</v>
+      </c>
+      <c r="AJ66" s="8" t="n">
+        <v>0.0025429</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -7575,6 +8165,15 @@
       <c r="AG67" s="8" t="n">
         <v>0.00335078</v>
       </c>
+      <c r="AH67" s="6" t="n">
+        <v>243197</v>
+      </c>
+      <c r="AI67" s="7" t="n">
+        <v>9626.219999999999</v>
+      </c>
+      <c r="AJ67" s="8" t="n">
+        <v>0.00323195</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -7682,6 +8281,15 @@
       <c r="AG68" s="8" t="n">
         <v>0.00203941</v>
       </c>
+      <c r="AH68" s="6" t="n">
+        <v>7962774</v>
+      </c>
+      <c r="AI68" s="7" t="n">
+        <v>4683.7</v>
+      </c>
+      <c r="AJ68" s="8" t="n">
+        <v>0.00157253</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -7789,6 +8397,15 @@
       <c r="AG69" s="8" t="n">
         <v>0.00253938</v>
       </c>
+      <c r="AH69" s="6" t="n">
+        <v>1300497</v>
+      </c>
+      <c r="AI69" s="7" t="n">
+        <v>7300.34</v>
+      </c>
+      <c r="AJ69" s="8" t="n">
+        <v>0.00245105</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -7896,6 +8513,15 @@
       <c r="AG70" s="8" t="n">
         <v>0.00218202</v>
       </c>
+      <c r="AH70" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ70" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -8003,6 +8629,15 @@
       <c r="AG71" s="8" t="n">
         <v>0.00197586</v>
       </c>
+      <c r="AH71" s="6" t="n">
+        <v>3100714</v>
+      </c>
+      <c r="AI71" s="7" t="n">
+        <v>5970.42</v>
+      </c>
+      <c r="AJ71" s="8" t="n">
+        <v>0.00200454</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8110,6 +8745,15 @@
       <c r="AG72" s="8" t="n">
         <v>0.0016107</v>
       </c>
+      <c r="AH72" s="6" t="n">
+        <v>4343422</v>
+      </c>
+      <c r="AI72" s="7" t="n">
+        <v>5098.74</v>
+      </c>
+      <c r="AJ72" s="8" t="n">
+        <v>0.00171187</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -8217,6 +8861,15 @@
       <c r="AG73" s="8" t="n">
         <v>0.00189655</v>
       </c>
+      <c r="AH73" s="6" t="n">
+        <v>362211</v>
+      </c>
+      <c r="AI73" s="7" t="n">
+        <v>5756.26</v>
+      </c>
+      <c r="AJ73" s="8" t="n">
+        <v>0.00193263</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8324,6 +8977,15 @@
       <c r="AG74" s="8" t="n">
         <v>0.00186307</v>
       </c>
+      <c r="AH74" s="6" t="n">
+        <v>2026624</v>
+      </c>
+      <c r="AI74" s="7" t="n">
+        <v>5155.73</v>
+      </c>
+      <c r="AJ74" s="8" t="n">
+        <v>0.00173101</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -8431,6 +9093,15 @@
       <c r="AG75" s="8" t="n">
         <v>0.00174252</v>
       </c>
+      <c r="AH75" s="6" t="n">
+        <v>107059</v>
+      </c>
+      <c r="AI75" s="7" t="n">
+        <v>5362.05</v>
+      </c>
+      <c r="AJ75" s="8" t="n">
+        <v>0.00180028</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8538,6 +9209,15 @@
       <c r="AG76" s="8" t="n">
         <v>0.0018583</v>
       </c>
+      <c r="AH76" s="6" t="n">
+        <v>503950</v>
+      </c>
+      <c r="AI76" s="7" t="n">
+        <v>4893.35</v>
+      </c>
+      <c r="AJ76" s="8" t="n">
+        <v>0.00164292</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -8645,6 +9325,15 @@
       <c r="AG77" s="8" t="n">
         <v>0.00196757</v>
       </c>
+      <c r="AH77" s="6" t="n">
+        <v>1859681</v>
+      </c>
+      <c r="AI77" s="7" t="n">
+        <v>5772.45</v>
+      </c>
+      <c r="AJ77" s="8" t="n">
+        <v>0.00193807</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -8752,6 +9441,15 @@
       <c r="AG78" s="8" t="n">
         <v>0.00147078</v>
       </c>
+      <c r="AH78" s="6" t="n">
+        <v>503579</v>
+      </c>
+      <c r="AI78" s="7" t="n">
+        <v>4255.75</v>
+      </c>
+      <c r="AJ78" s="8" t="n">
+        <v>0.00142884</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -8859,6 +9557,15 @@
       <c r="AG79" s="8" t="n">
         <v>0.00166281</v>
       </c>
+      <c r="AH79" s="6" t="n">
+        <v>1649942</v>
+      </c>
+      <c r="AI79" s="7" t="n">
+        <v>4555.49</v>
+      </c>
+      <c r="AJ79" s="8" t="n">
+        <v>0.00152948</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -8966,6 +9673,15 @@
       <c r="AG80" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH80" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -9073,6 +9789,15 @@
       <c r="AG81" s="8" t="n">
         <v>0.00138753</v>
       </c>
+      <c r="AH81" s="6" t="n">
+        <v>5087689</v>
+      </c>
+      <c r="AI81" s="7" t="n">
+        <v>2678.67</v>
+      </c>
+      <c r="AJ81" s="8" t="n">
+        <v>0.00089935</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -9180,6 +9905,15 @@
       <c r="AG82" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH82" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ82" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9287,6 +10021,15 @@
       <c r="AG83" s="8" t="n">
         <v>0.00100891</v>
       </c>
+      <c r="AH83" s="6" t="n">
+        <v>2041368</v>
+      </c>
+      <c r="AI83" s="7" t="n">
+        <v>2102.61</v>
+      </c>
+      <c r="AJ83" s="8" t="n">
+        <v>0.0007059400000000001</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -9394,6 +10137,15 @@
       <c r="AG84" s="8" t="n">
         <v>0.00114345</v>
       </c>
+      <c r="AH84" s="6" t="n">
+        <v>2095455</v>
+      </c>
+      <c r="AI84" s="7" t="n">
+        <v>3287.35</v>
+      </c>
+      <c r="AJ84" s="8" t="n">
+        <v>0.00110371</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -9501,6 +10253,15 @@
       <c r="AG85" s="8" t="n">
         <v>0.00125428</v>
       </c>
+      <c r="AH85" s="6" t="n">
+        <v>865732</v>
+      </c>
+      <c r="AI85" s="7" t="n">
+        <v>3788.01</v>
+      </c>
+      <c r="AJ85" s="8" t="n">
+        <v>0.0012718</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -9608,6 +10369,15 @@
       <c r="AG86" s="8" t="n">
         <v>0.0010516</v>
       </c>
+      <c r="AH86" s="6" t="n">
+        <v>999412</v>
+      </c>
+      <c r="AI86" s="7" t="n">
+        <v>3090.18</v>
+      </c>
+      <c r="AJ86" s="8" t="n">
+        <v>0.00103751</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -9715,6 +10485,15 @@
       <c r="AG87" s="8" t="n">
         <v>0.0009783000000000001</v>
       </c>
+      <c r="AH87" s="6" t="n">
+        <v>1143581</v>
+      </c>
+      <c r="AI87" s="7" t="n">
+        <v>5578.96</v>
+      </c>
+      <c r="AJ87" s="8" t="n">
+        <v>0.00187311</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -9822,6 +10601,15 @@
       <c r="AG88" s="8" t="n">
         <v>0.00092948</v>
       </c>
+      <c r="AH88" s="6" t="n">
+        <v>63911</v>
+      </c>
+      <c r="AI88" s="7" t="n">
+        <v>2612.17</v>
+      </c>
+      <c r="AJ88" s="8" t="n">
+        <v>0.0008770200000000001</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -9929,6 +10717,15 @@
       <c r="AG89" s="8" t="n">
         <v>0.00101164</v>
       </c>
+      <c r="AH89" s="6" t="n">
+        <v>769177</v>
+      </c>
+      <c r="AI89" s="7" t="n">
+        <v>3134.4</v>
+      </c>
+      <c r="AJ89" s="8" t="n">
+        <v>0.00105236</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -10036,6 +10833,15 @@
       <c r="AG90" s="8" t="n">
         <v>0.00125856</v>
       </c>
+      <c r="AH90" s="6" t="n">
+        <v>2669275</v>
+      </c>
+      <c r="AI90" s="7" t="n">
+        <v>3526.11</v>
+      </c>
+      <c r="AJ90" s="8" t="n">
+        <v>0.00118387</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -10143,6 +10949,15 @@
       <c r="AG91" s="8" t="n">
         <v>0.0009621499999999999</v>
       </c>
+      <c r="AH91" s="6" t="n">
+        <v>95108</v>
+      </c>
+      <c r="AI91" s="7" t="n">
+        <v>2831.27</v>
+      </c>
+      <c r="AJ91" s="8" t="n">
+        <v>0.00095058</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10250,6 +11065,15 @@
       <c r="AG92" s="8" t="n">
         <v>0.00049967</v>
       </c>
+      <c r="AH92" s="6" t="n">
+        <v>672534</v>
+      </c>
+      <c r="AI92" s="7" t="n">
+        <v>1299.07</v>
+      </c>
+      <c r="AJ92" s="8" t="n">
+        <v>0.00043615</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -10357,6 +11181,15 @@
       <c r="AG93" s="8" t="n">
         <v>0.00066532</v>
       </c>
+      <c r="AH93" s="6" t="n">
+        <v>500000</v>
+      </c>
+      <c r="AI93" s="7" t="n">
+        <v>1903.5</v>
+      </c>
+      <c r="AJ93" s="8" t="n">
+        <v>0.0006390899999999999</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -10464,6 +11297,15 @@
       <c r="AG94" s="8" t="n">
         <v>0.00038833</v>
       </c>
+      <c r="AH94" s="6" t="n">
+        <v>4556962</v>
+      </c>
+      <c r="AI94" s="7" t="n">
+        <v>1090.94</v>
+      </c>
+      <c r="AJ94" s="8" t="n">
+        <v>0.00036628</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -10571,6 +11413,15 @@
       <c r="AG95" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH95" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ95" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -10678,6 +11529,15 @@
       <c r="AG96" s="8" t="n">
         <v>5.087999999999999e-05</v>
       </c>
+      <c r="AH96" s="6" t="n">
+        <v>140571</v>
+      </c>
+      <c r="AI96" s="7" t="n">
+        <v>137.11</v>
+      </c>
+      <c r="AJ96" s="8" t="n">
+        <v>4.603e-05</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -10785,6 +11645,15 @@
       <c r="AG97" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH97" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -10892,6 +11761,15 @@
       <c r="AG98" s="8" t="n">
         <v>0.00112035</v>
       </c>
+      <c r="AH98" s="6" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="AI98" s="7" t="n">
+        <v>3396.58</v>
+      </c>
+      <c r="AJ98" s="8" t="n">
+        <v>0.00114038</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -10999,6 +11877,15 @@
       <c r="AG99" s="8" t="n">
         <v>0.00098551</v>
       </c>
+      <c r="AH99" s="6" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="AI99" s="7" t="n">
+        <v>2987.98</v>
+      </c>
+      <c r="AJ99" s="8" t="n">
+        <v>0.0010032</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -11106,6 +11993,15 @@
       <c r="AG100" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH100" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -11213,6 +12109,15 @@
       <c r="AG101" s="8" t="n">
         <v>0.00082454</v>
       </c>
+      <c r="AH101" s="6" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="AI101" s="7" t="n">
+        <v>2499.64</v>
+      </c>
+      <c r="AJ101" s="8" t="n">
+        <v>0.00083924</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11320,6 +12225,15 @@
       <c r="AG102" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH102" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI102" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ102" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -11427,6 +12341,15 @@
       <c r="AG103" s="8" t="n">
         <v>0.0006611</v>
       </c>
+      <c r="AH103" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ103" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -11534,6 +12457,15 @@
       <c r="AG104" s="8" t="n">
         <v>0.00032879</v>
       </c>
+      <c r="AH104" s="6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AI104" s="7" t="n">
+        <v>996.8200000000001</v>
+      </c>
+      <c r="AJ104" s="8" t="n">
+        <v>0.00033468</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -11641,6 +12573,15 @@
       <c r="AG105" s="8" t="n">
         <v>2.02e-05</v>
       </c>
+      <c r="AH105" s="6" t="n">
+        <v>499975</v>
+      </c>
+      <c r="AI105" s="7" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="AJ105" s="8" t="n">
+        <v>2.052e-05</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11748,6 +12689,15 @@
       <c r="AG106" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH106" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ106" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -11855,6 +12805,15 @@
       <c r="AG107" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH107" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ107" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11962,6 +12921,15 @@
       <c r="AG108" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH108" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ108" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -12069,6 +13037,15 @@
       <c r="AG109" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH109" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ109" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -12176,6 +13153,15 @@
       <c r="AG110" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH110" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI110" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ110" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12283,6 +13269,15 @@
       <c r="AG111" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH111" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12390,6 +13385,15 @@
       <c r="AG112" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH112" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI112" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ112" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12497,6 +13501,15 @@
       <c r="AG113" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH113" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ113" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12604,6 +13617,15 @@
       <c r="AG114" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH114" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI114" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ114" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -12711,6 +13733,15 @@
       <c r="AG115" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH115" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI115" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ115" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -12818,6 +13849,15 @@
       <c r="AG116" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH116" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -12925,6 +13965,15 @@
       <c r="AG117" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH117" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI117" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ117" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -13032,6 +14081,15 @@
       <c r="AG118" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH118" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI118" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ118" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -13139,6 +14197,15 @@
       <c r="AG119" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH119" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI119" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ119" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -13246,6 +14313,15 @@
       <c r="AG120" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH120" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI120" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ120" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -13353,6 +14429,15 @@
       <c r="AG121" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH121" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI121" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ121" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -13460,6 +14545,15 @@
       <c r="AG122" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH122" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI122" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ122" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13567,6 +14661,15 @@
       <c r="AG123" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH123" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI123" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ123" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -13674,6 +14777,15 @@
       <c r="AG124" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH124" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI124" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ124" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13781,6 +14893,15 @@
       <c r="AG125" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH125" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI125" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ125" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -13888,6 +15009,15 @@
       <c r="AG126" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH126" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ126" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -13995,6 +15125,15 @@
       <c r="AG127" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH127" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI127" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ127" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -14102,6 +15241,15 @@
       <c r="AG128" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH128" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ128" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -14209,6 +15357,15 @@
       <c r="AG129" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH129" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ129" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -14316,6 +15473,15 @@
       <c r="AG130" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH130" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI130" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ130" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -14423,6 +15589,15 @@
       <c r="AG131" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH131" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI131" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ131" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -14530,6 +15705,15 @@
       <c r="AG132" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH132" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ132" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -14637,6 +15821,15 @@
       <c r="AG133" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH133" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -14744,6 +15937,15 @@
       <c r="AG134" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH134" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI134" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ134" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -14851,6 +16053,15 @@
       <c r="AG135" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH135" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ135" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -14958,6 +16169,15 @@
       <c r="AG136" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH136" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ136" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -15065,6 +16285,15 @@
       <c r="AG137" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH137" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -15172,6 +16401,15 @@
       <c r="AG138" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH138" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ138" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -15279,6 +16517,15 @@
       <c r="AG139" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH139" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ139" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -15386,6 +16633,15 @@
       <c r="AG140" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH140" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ140" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -15493,6 +16749,15 @@
       <c r="AG141" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH141" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI141" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ141" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -15600,6 +16865,15 @@
       <c r="AG142" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH142" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI142" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ142" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -15707,6 +16981,15 @@
       <c r="AG143" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH143" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI143" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ143" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -15814,6 +17097,15 @@
       <c r="AG144" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH144" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ144" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -15921,6 +17213,15 @@
       <c r="AG145" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH145" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI145" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ145" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -16028,6 +17329,15 @@
       <c r="AG146" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH146" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI146" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ146" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -16135,6 +17445,15 @@
       <c r="AG147" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH147" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI147" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ147" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -16242,6 +17561,15 @@
       <c r="AG148" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH148" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI148" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ148" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -16349,6 +17677,15 @@
       <c r="AG149" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH149" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI149" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ149" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -16456,6 +17793,15 @@
       <c r="AG150" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH150" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI150" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ150" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -16563,6 +17909,15 @@
       <c r="AG151" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH151" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -16670,6 +18025,15 @@
       <c r="AG152" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH152" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI152" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ152" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -16777,6 +18141,15 @@
       <c r="AG153" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH153" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI153" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ153" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -16884,6 +18257,15 @@
       <c r="AG154" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH154" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI154" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ154" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -16991,6 +18373,15 @@
       <c r="AG155" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH155" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI155" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ155" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -17098,6 +18489,15 @@
       <c r="AG156" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH156" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI156" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ156" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -17205,6 +18605,15 @@
       <c r="AG157" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH157" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -17312,6 +18721,15 @@
       <c r="AG158" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH158" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ158" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -17419,6 +18837,15 @@
       <c r="AG159" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH159" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI159" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ159" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -17526,6 +18953,15 @@
       <c r="AG160" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH160" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI160" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ160" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -17633,6 +19069,15 @@
       <c r="AG161" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH161" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI161" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ161" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -17740,6 +19185,15 @@
       <c r="AG162" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH162" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI162" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -17847,6 +19301,15 @@
       <c r="AG163" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH163" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI163" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ163" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -17954,6 +19417,15 @@
       <c r="AG164" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH164" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI164" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ164" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -18061,6 +19533,15 @@
       <c r="AG165" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH165" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI165" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -18168,6 +19649,15 @@
       <c r="AG166" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH166" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI166" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ166" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -18275,6 +19765,15 @@
       <c r="AG167" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH167" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI167" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ167" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -18382,21 +19881,30 @@
       <c r="AG168" s="8" t="n">
         <v>0</v>
       </c>
+      <c r="AH168" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI168" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ168" s="8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
         <is>
-          <t>IRB Infrastructure Developers Limited</t>
+          <t>Adani Green Energy Limited</t>
         </is>
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>INE821I01022</t>
+          <t>INE364U01010</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="D169" s="6" t="n">
@@ -18481,29 +19989,38 @@
         <v>0</v>
       </c>
       <c r="AE169" s="6" t="n">
-        <v>33637792</v>
+        <v>0</v>
       </c>
       <c r="AF169" s="7" t="n">
-        <v>14433.98</v>
+        <v>0</v>
       </c>
       <c r="AG169" s="8" t="n">
-        <v>0.00478426</v>
+        <v>0</v>
+      </c>
+      <c r="AH169" s="6" t="n">
+        <v>5436317</v>
+      </c>
+      <c r="AI169" s="7" t="n">
+        <v>55184.05</v>
+      </c>
+      <c r="AJ169" s="8" t="n">
+        <v>0.01852774</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
         <is>
-          <t>Black Box Limited</t>
+          <t>HDFC Life Insurance Co Ltd</t>
         </is>
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>INE676A01027</t>
+          <t>INE795G01014</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>IT - Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D170" s="6" t="n">
@@ -18588,29 +20105,38 @@
         <v>0</v>
       </c>
       <c r="AE170" s="6" t="n">
-        <v>1783891</v>
+        <v>0</v>
       </c>
       <c r="AF170" s="7" t="n">
-        <v>9522.41</v>
+        <v>0</v>
       </c>
       <c r="AG170" s="8" t="n">
-        <v>0.00315628</v>
+        <v>0</v>
+      </c>
+      <c r="AH170" s="6" t="n">
+        <v>2323077</v>
+      </c>
+      <c r="AI170" s="7" t="n">
+        <v>17419.59</v>
+      </c>
+      <c r="AJ170" s="8" t="n">
+        <v>0.005848529999999999</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
         <is>
-          <t>Graphite India Limited</t>
+          <t>IRB Infrastructure Developers Limited</t>
         </is>
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>INE371A01025</t>
+          <t>INE821I01022</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>Industrial Products</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D171" s="6" t="n">
@@ -18695,29 +20221,38 @@
         <v>0</v>
       </c>
       <c r="AE171" s="6" t="n">
-        <v>454292</v>
+        <v>33637792</v>
       </c>
       <c r="AF171" s="7" t="n">
-        <v>2521.32</v>
+        <v>14433.98</v>
       </c>
       <c r="AG171" s="8" t="n">
-        <v>0.00083571</v>
+        <v>0.00478426</v>
+      </c>
+      <c r="AH171" s="6" t="n">
+        <v>33637792</v>
+      </c>
+      <c r="AI171" s="7" t="n">
+        <v>14144.69</v>
+      </c>
+      <c r="AJ171" s="8" t="n">
+        <v>0.004749</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
         <is>
-          <t>Adani Enterprises Limited Rights</t>
+          <t>Black Box Limited</t>
         </is>
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>INE423A20016</t>
+          <t>INE676A01027</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>N.A.</t>
+          <t>IT - Services</t>
         </is>
       </c>
       <c r="D172" s="6" t="n">
@@ -18802,29 +20337,38 @@
         <v>0</v>
       </c>
       <c r="AE172" s="6" t="n">
-        <v>296195</v>
+        <v>1783891</v>
       </c>
       <c r="AF172" s="7" t="n">
-        <v>1310.37</v>
+        <v>9522.41</v>
       </c>
       <c r="AG172" s="8" t="n">
-        <v>0.00043433</v>
+        <v>0.00315628</v>
+      </c>
+      <c r="AH172" s="6" t="n">
+        <v>1810683</v>
+      </c>
+      <c r="AI172" s="7" t="n">
+        <v>9974.15</v>
+      </c>
+      <c r="AJ172" s="8" t="n">
+        <v>0.00334876</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
         <is>
-          <t>Sumitomo Chemical India Limited</t>
+          <t>S. P. Apparels Limited</t>
         </is>
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>INE258G01013</t>
+          <t>INE212I01016</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>Fertilizers &amp; Agrochemicals</t>
+          <t>Textiles &amp; Apparels</t>
         </is>
       </c>
       <c r="D173" s="6" t="n">
@@ -18909,24 +20453,33 @@
         <v>0</v>
       </c>
       <c r="AE173" s="6" t="n">
-        <v>201956</v>
+        <v>0</v>
       </c>
       <c r="AF173" s="7" t="n">
-        <v>941.11</v>
+        <v>0</v>
       </c>
       <c r="AG173" s="8" t="n">
-        <v>0.00031194</v>
+        <v>0</v>
+      </c>
+      <c r="AH173" s="6" t="n">
+        <v>805180</v>
+      </c>
+      <c r="AI173" s="7" t="n">
+        <v>5655.58</v>
+      </c>
+      <c r="AJ173" s="8" t="n">
+        <v>0.00189883</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
-          <t>MIDCAPNIFTY 30/12/2025</t>
+          <t>Adani Enterprises Limited PP RE</t>
         </is>
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>MIDCPNIFTY301225</t>
+          <t>IN9423A01030</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
@@ -19016,29 +20569,38 @@
         <v>0</v>
       </c>
       <c r="AE174" s="6" t="n">
-        <v>652260</v>
+        <v>0</v>
       </c>
       <c r="AF174" s="7" t="n">
-        <v>92134.00999999999</v>
+        <v>0</v>
       </c>
       <c r="AG174" s="8" t="n">
-        <v>0.03053858</v>
+        <v>0</v>
+      </c>
+      <c r="AH174" s="6" t="n">
+        <v>296195</v>
+      </c>
+      <c r="AI174" s="7" t="n">
+        <v>3968.12</v>
+      </c>
+      <c r="AJ174" s="8" t="n">
+        <v>0.00133228</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
         <is>
-          <t>Samvardhana Motherson International Ltd 30/12/2025</t>
+          <t>Graphite India Limited</t>
         </is>
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>MOTHERSON301225</t>
+          <t>INE371A01025</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Industrial Products</t>
         </is>
       </c>
       <c r="D175" s="6" t="n">
@@ -19123,29 +20685,38 @@
         <v>0</v>
       </c>
       <c r="AE175" s="6" t="n">
-        <v>6266850</v>
+        <v>454292</v>
       </c>
       <c r="AF175" s="7" t="n">
-        <v>7322.81</v>
+        <v>2521.32</v>
       </c>
       <c r="AG175" s="8" t="n">
-        <v>0.00242721</v>
+        <v>0.00083571</v>
+      </c>
+      <c r="AH175" s="6" t="n">
+        <v>454292</v>
+      </c>
+      <c r="AI175" s="7" t="n">
+        <v>2915.19</v>
+      </c>
+      <c r="AJ175" s="8" t="n">
+        <v>0.00097876</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
         <is>
-          <t>182 Days Treasury Bill 29-Jan-2026</t>
+          <t>Ravindra Energy Limited</t>
         </is>
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>IN002025Y180</t>
+          <t>INE206N01018</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>N.A.</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="D176" s="6" t="n">
@@ -19230,29 +20801,38 @@
         <v>0</v>
       </c>
       <c r="AE176" s="6" t="n">
-        <v>2600000</v>
+        <v>0</v>
       </c>
       <c r="AF176" s="7" t="n">
-        <v>2576.83</v>
+        <v>0</v>
       </c>
       <c r="AG176" s="8" t="n">
-        <v>0.00085411</v>
+        <v>0</v>
+      </c>
+      <c r="AH176" s="6" t="n">
+        <v>700000</v>
+      </c>
+      <c r="AI176" s="7" t="n">
+        <v>1112.02</v>
+      </c>
+      <c r="AJ176" s="8" t="n">
+        <v>0.00037335</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
         <is>
-          <t>91 Days Treasury Bill 25-Dec-2025</t>
+          <t>Sumitomo Chemical India Limited</t>
         </is>
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>IN002025X265</t>
+          <t>INE258G01013</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>N.A.</t>
+          <t>Fertilizers &amp; Agrochemicals</t>
         </is>
       </c>
       <c r="D177" s="6" t="n">
@@ -19337,29 +20917,38 @@
         <v>0</v>
       </c>
       <c r="AE177" s="6" t="n">
-        <v>2000000</v>
+        <v>201956</v>
       </c>
       <c r="AF177" s="7" t="n">
-        <v>1992.58</v>
+        <v>941.11</v>
       </c>
       <c r="AG177" s="8" t="n">
-        <v>0.00066046</v>
+        <v>0.00031194</v>
+      </c>
+      <c r="AH177" s="6" t="n">
+        <v>201956</v>
+      </c>
+      <c r="AI177" s="7" t="n">
+        <v>951.21</v>
+      </c>
+      <c r="AJ177" s="8" t="n">
+        <v>0.00031936</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
         <is>
-          <t>91 Days Treasury Bill 26-Feb-2026</t>
+          <t>National Building Construction Corp Ltd. 27/01/2026</t>
         </is>
       </c>
       <c r="B178" s="4" t="inlineStr">
         <is>
-          <t>IN002025X356</t>
+          <t>NBCC270126</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>N.A.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D178" s="6" t="n">
@@ -19444,24 +21033,33 @@
         <v>0</v>
       </c>
       <c r="AE178" s="6" t="n">
-        <v>2000000</v>
+        <v>0</v>
       </c>
       <c r="AF178" s="7" t="n">
-        <v>1974.39</v>
+        <v>0</v>
       </c>
       <c r="AG178" s="8" t="n">
-        <v>0.00065443</v>
+        <v>0</v>
+      </c>
+      <c r="AH178" s="6" t="n">
+        <v>8229000</v>
+      </c>
+      <c r="AI178" s="7" t="n">
+        <v>10059.95</v>
+      </c>
+      <c r="AJ178" s="8" t="n">
+        <v>0.00337757</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
         <is>
-          <t>TREPS 01-Dec-2025 DEPO 10</t>
+          <t>182 Days Treasury Bill 29-Jan-2026</t>
         </is>
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>INCBLO011225</t>
+          <t>IN002025Y180</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
@@ -19551,24 +21149,33 @@
         <v>0</v>
       </c>
       <c r="AE179" s="6" t="n">
-        <v>2041142.8</v>
+        <v>2600000</v>
       </c>
       <c r="AF179" s="7" t="n">
-        <v>204053.67</v>
+        <v>2576.83</v>
       </c>
       <c r="AG179" s="8" t="n">
-        <v>0.06763528000000001</v>
+        <v>0.00085411</v>
+      </c>
+      <c r="AH179" s="6" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="AI179" s="7" t="n">
+        <v>2589.57</v>
+      </c>
+      <c r="AJ179" s="8" t="n">
+        <v>0.00086943</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
         <is>
-          <t>Aditya Birla Lifestyle Brands Limited</t>
+          <t>91 Days Treasury Bill 26-Feb-2026</t>
         </is>
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>INPYEQADBA01</t>
+          <t>IN002025X356</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
@@ -19613,13 +21220,13 @@
         <v>0</v>
       </c>
       <c r="P180" s="6" t="n">
-        <v>32212218</v>
+        <v>0</v>
       </c>
       <c r="Q180" s="7" t="n">
-        <v>55066.79</v>
+        <v>0</v>
       </c>
       <c r="R180" s="8" t="n">
-        <v>0.01952362</v>
+        <v>0</v>
       </c>
       <c r="S180" s="6" t="n">
         <v>0</v>
@@ -19658,29 +21265,38 @@
         <v>0</v>
       </c>
       <c r="AE180" s="6" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="AF180" s="7" t="n">
-        <v>0</v>
+        <v>1974.39</v>
       </c>
       <c r="AG180" s="8" t="n">
-        <v>0</v>
+        <v>0.00065443</v>
+      </c>
+      <c r="AH180" s="6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AI180" s="7" t="n">
+        <v>1984.2</v>
+      </c>
+      <c r="AJ180" s="8" t="n">
+        <v>0.0006661799999999999</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>ITC Limited</t>
+          <t>TREPS 01-Jan-2026 DEPO 10</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>INE154A01025</t>
+          <t>INCBLO010126</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>Diversified FMCG</t>
+          <t>N.A.</t>
         </is>
       </c>
       <c r="D181" s="6" t="n">
@@ -19720,13 +21336,13 @@
         <v>0</v>
       </c>
       <c r="P181" s="6" t="n">
-        <v>349060</v>
+        <v>0</v>
       </c>
       <c r="Q181" s="7" t="n">
-        <v>1459.25</v>
+        <v>0</v>
       </c>
       <c r="R181" s="8" t="n">
-        <v>0.00051737</v>
+        <v>0</v>
       </c>
       <c r="S181" s="6" t="n">
         <v>0</v>
@@ -19772,22 +21388,31 @@
       </c>
       <c r="AG181" s="8" t="n">
         <v>0</v>
+      </c>
+      <c r="AH181" s="6" t="n">
+        <v>1557986.2</v>
+      </c>
+      <c r="AI181" s="7" t="n">
+        <v>155798.62</v>
+      </c>
+      <c r="AJ181" s="8" t="n">
+        <v>0.05230853</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
         <is>
-          <t>Oil and Natural Gas Corporation Ltd. 26/06/2025</t>
+          <t>Adani Enterprises Limited Rights</t>
         </is>
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>ONGC260625</t>
+          <t>INE423A20016</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>N.A.</t>
         </is>
       </c>
       <c r="D182" s="6" t="n">
@@ -19827,13 +21452,13 @@
         <v>0</v>
       </c>
       <c r="P182" s="6" t="n">
-        <v>8387225</v>
+        <v>0</v>
       </c>
       <c r="Q182" s="7" t="n">
-        <v>20198.12</v>
+        <v>0</v>
       </c>
       <c r="R182" s="8" t="n">
-        <v>0.00716113</v>
+        <v>0</v>
       </c>
       <c r="S182" s="6" t="n">
         <v>0</v>
@@ -19872,29 +21497,38 @@
         <v>0</v>
       </c>
       <c r="AE182" s="6" t="n">
-        <v>0</v>
+        <v>296195</v>
       </c>
       <c r="AF182" s="7" t="n">
-        <v>0</v>
+        <v>1310.37</v>
       </c>
       <c r="AG182" s="8" t="n">
+        <v>0.00043433</v>
+      </c>
+      <c r="AH182" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI182" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ182" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
         <is>
-          <t>National Building Construction Corp 26/06/2025</t>
+          <t>MIDCAPNIFTY 30/12/2025</t>
         </is>
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>NBCC260625</t>
+          <t>MIDCPNIFTY301225</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>N.A.</t>
         </is>
       </c>
       <c r="D183" s="6" t="n">
@@ -19934,13 +21568,13 @@
         <v>0</v>
       </c>
       <c r="P183" s="6" t="n">
-        <v>4036800</v>
+        <v>0</v>
       </c>
       <c r="Q183" s="7" t="n">
-        <v>5009.67</v>
+        <v>0</v>
       </c>
       <c r="R183" s="8" t="n">
-        <v>0.00177615</v>
+        <v>0</v>
       </c>
       <c r="S183" s="6" t="n">
         <v>0</v>
@@ -19979,29 +21613,38 @@
         <v>0</v>
       </c>
       <c r="AE183" s="6" t="n">
-        <v>0</v>
+        <v>652260</v>
       </c>
       <c r="AF183" s="7" t="n">
-        <v>0</v>
+        <v>92134.00999999999</v>
       </c>
       <c r="AG183" s="8" t="n">
+        <v>0.03053858</v>
+      </c>
+      <c r="AH183" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI183" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ183" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
         <is>
-          <t>NCC Ltd 26/06/2025</t>
+          <t>Samvardhana Motherson International Ltd 30/12/2025</t>
         </is>
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>NCC260625</t>
+          <t>MOTHERSON301225</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="D184" s="6" t="n">
@@ -20041,13 +21684,13 @@
         <v>0</v>
       </c>
       <c r="P184" s="6" t="n">
-        <v>1654300</v>
+        <v>0</v>
       </c>
       <c r="Q184" s="7" t="n">
-        <v>3835.16</v>
+        <v>0</v>
       </c>
       <c r="R184" s="8" t="n">
-        <v>0.00135974</v>
+        <v>0</v>
       </c>
       <c r="S184" s="6" t="n">
         <v>0</v>
@@ -20086,29 +21729,38 @@
         <v>0</v>
       </c>
       <c r="AE184" s="6" t="n">
-        <v>0</v>
+        <v>6266850</v>
       </c>
       <c r="AF184" s="7" t="n">
-        <v>0</v>
+        <v>7322.81</v>
       </c>
       <c r="AG184" s="8" t="n">
+        <v>0.00242721</v>
+      </c>
+      <c r="AH184" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI184" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ184" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
         <is>
-          <t>Chambal Fertilizers &amp; Chemicals Ltd 26/06/2025</t>
+          <t>91 Days Treasury Bill 25-Dec-2025</t>
         </is>
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>CHAMBLFERT260625</t>
+          <t>IN002025X265</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>Fertilizers &amp; Agrochemicals</t>
+          <t>N.A.</t>
         </is>
       </c>
       <c r="D185" s="6" t="n">
@@ -20148,13 +21800,13 @@
         <v>0</v>
       </c>
       <c r="P185" s="6" t="n">
-        <v>513000</v>
+        <v>0</v>
       </c>
       <c r="Q185" s="7" t="n">
-        <v>2846.89</v>
+        <v>0</v>
       </c>
       <c r="R185" s="8" t="n">
-        <v>0.00100935</v>
+        <v>0</v>
       </c>
       <c r="S185" s="6" t="n">
         <v>0</v>
@@ -20193,24 +21845,33 @@
         <v>0</v>
       </c>
       <c r="AE185" s="6" t="n">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="AF185" s="7" t="n">
-        <v>0</v>
+        <v>1992.58</v>
       </c>
       <c r="AG185" s="8" t="n">
+        <v>0.00066046</v>
+      </c>
+      <c r="AH185" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI185" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ185" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
         <is>
-          <t>TREPS 02-Jun-2025 DEPO 10</t>
+          <t>TREPS 01-Dec-2025 DEPO 10</t>
         </is>
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>INCBLO020625</t>
+          <t>INCBLO011225</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
@@ -20255,13 +21916,13 @@
         <v>0</v>
       </c>
       <c r="P186" s="6" t="n">
-        <v>1827102.8</v>
+        <v>0</v>
       </c>
       <c r="Q186" s="7" t="n">
-        <v>182652.41</v>
+        <v>0</v>
       </c>
       <c r="R186" s="8" t="n">
-        <v>0.06475838</v>
+        <v>0</v>
       </c>
       <c r="S186" s="6" t="n">
         <v>0</v>
@@ -20300,29 +21961,38 @@
         <v>0</v>
       </c>
       <c r="AE186" s="6" t="n">
-        <v>0</v>
+        <v>2041142.8</v>
       </c>
       <c r="AF186" s="7" t="n">
-        <v>0</v>
+        <v>204053.67</v>
       </c>
       <c r="AG186" s="8" t="n">
+        <v>0.06763528000000001</v>
+      </c>
+      <c r="AH186" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI186" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ186" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
         <is>
-          <t>Larsen &amp; Toubro Limited 27/03/2025</t>
+          <t>Aditya Birla Lifestyle Brands Limited</t>
         </is>
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>LT270325</t>
+          <t>INPYEQADBA01</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>N.A.</t>
         </is>
       </c>
       <c r="D187" s="6" t="n">
@@ -20335,13 +22005,13 @@
         <v>0</v>
       </c>
       <c r="G187" s="6" t="n">
-        <v>1071000</v>
+        <v>0</v>
       </c>
       <c r="H187" s="7" t="n">
-        <v>34073.87</v>
+        <v>0</v>
       </c>
       <c r="I187" s="8" t="n">
-        <v>0.01492346</v>
+        <v>0</v>
       </c>
       <c r="J187" s="6" t="n">
         <v>0</v>
@@ -20362,13 +22032,13 @@
         <v>0</v>
       </c>
       <c r="P187" s="6" t="n">
-        <v>0</v>
+        <v>32212218</v>
       </c>
       <c r="Q187" s="7" t="n">
-        <v>0</v>
+        <v>55066.79</v>
       </c>
       <c r="R187" s="8" t="n">
-        <v>0</v>
+        <v>0.01952362</v>
       </c>
       <c r="S187" s="6" t="n">
         <v>0</v>
@@ -20413,23 +22083,32 @@
         <v>0</v>
       </c>
       <c r="AG187" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI187" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
         <is>
-          <t>Oil and Natural Gas Corporation Ltd. 27/03/2025</t>
+          <t>ITC Limited</t>
         </is>
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>ONGC270325</t>
+          <t>INE154A01025</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>Oil</t>
+          <t>Diversified FMCG</t>
         </is>
       </c>
       <c r="D188" s="6" t="n">
@@ -20442,13 +22121,13 @@
         <v>0</v>
       </c>
       <c r="G188" s="6" t="n">
-        <v>8387225</v>
+        <v>0</v>
       </c>
       <c r="H188" s="7" t="n">
-        <v>19005.45</v>
+        <v>0</v>
       </c>
       <c r="I188" s="8" t="n">
-        <v>0.00832389</v>
+        <v>0</v>
       </c>
       <c r="J188" s="6" t="n">
         <v>0</v>
@@ -20469,13 +22148,13 @@
         <v>0</v>
       </c>
       <c r="P188" s="6" t="n">
-        <v>0</v>
+        <v>349060</v>
       </c>
       <c r="Q188" s="7" t="n">
-        <v>0</v>
+        <v>1459.25</v>
       </c>
       <c r="R188" s="8" t="n">
-        <v>0</v>
+        <v>0.00051737</v>
       </c>
       <c r="S188" s="6" t="n">
         <v>0</v>
@@ -20520,23 +22199,32 @@
         <v>0</v>
       </c>
       <c r="AG188" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH188" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI188" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ188" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
         <is>
-          <t>GAIL (India) Limited 27/03/2025</t>
+          <t>Oil and Natural Gas Corporation Ltd. 26/06/2025</t>
         </is>
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>GAIL270325</t>
+          <t>ONGC260625</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>Gas</t>
+          <t>Oil</t>
         </is>
       </c>
       <c r="D189" s="6" t="n">
@@ -20549,13 +22237,13 @@
         <v>0</v>
       </c>
       <c r="G189" s="6" t="n">
-        <v>2968050</v>
+        <v>0</v>
       </c>
       <c r="H189" s="7" t="n">
-        <v>4646.48</v>
+        <v>0</v>
       </c>
       <c r="I189" s="8" t="n">
-        <v>0.00203504</v>
+        <v>0</v>
       </c>
       <c r="J189" s="6" t="n">
         <v>0</v>
@@ -20576,13 +22264,13 @@
         <v>0</v>
       </c>
       <c r="P189" s="6" t="n">
-        <v>0</v>
+        <v>8387225</v>
       </c>
       <c r="Q189" s="7" t="n">
-        <v>0</v>
+        <v>20198.12</v>
       </c>
       <c r="R189" s="8" t="n">
-        <v>0</v>
+        <v>0.00716113</v>
       </c>
       <c r="S189" s="6" t="n">
         <v>0</v>
@@ -20627,23 +22315,32 @@
         <v>0</v>
       </c>
       <c r="AG189" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI189" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ189" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
         <is>
-          <t>TREPS 03-Mar-2025 DEPO 10</t>
+          <t>National Building Construction Corp 26/06/2025</t>
         </is>
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>INCBLO030325</t>
+          <t>NBCC260625</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>N.A.</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="D190" s="6" t="n">
@@ -20656,13 +22353,13 @@
         <v>0</v>
       </c>
       <c r="G190" s="6" t="n">
-        <v>1840647.9</v>
+        <v>0</v>
       </c>
       <c r="H190" s="7" t="n">
-        <v>184001.66</v>
+        <v>0</v>
       </c>
       <c r="I190" s="8" t="n">
-        <v>0.08058788</v>
+        <v>0</v>
       </c>
       <c r="J190" s="6" t="n">
         <v>0</v>
@@ -20683,13 +22380,13 @@
         <v>0</v>
       </c>
       <c r="P190" s="6" t="n">
-        <v>0</v>
+        <v>4036800</v>
       </c>
       <c r="Q190" s="7" t="n">
-        <v>0</v>
+        <v>5009.67</v>
       </c>
       <c r="R190" s="8" t="n">
-        <v>0</v>
+        <v>0.00177615</v>
       </c>
       <c r="S190" s="6" t="n">
         <v>0</v>
@@ -20734,111 +22431,941 @@
         <v>0</v>
       </c>
       <c r="AG190" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI190" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ190" s="8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="9" t="inlineStr">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>NCC Ltd 26/06/2025</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>NCC260625</t>
+        </is>
+      </c>
+      <c r="C191" s="5" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I191" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" s="6" t="n">
+        <v>1654300</v>
+      </c>
+      <c r="Q191" s="7" t="n">
+        <v>3835.16</v>
+      </c>
+      <c r="R191" s="8" t="n">
+        <v>0.00135974</v>
+      </c>
+      <c r="S191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T191" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U191" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W191" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X191" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z191" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA191" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC191" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD191" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF191" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG191" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH191" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI191" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ191" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="inlineStr">
+        <is>
+          <t>Chambal Fertilizers &amp; Chemicals Ltd 26/06/2025</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>CHAMBLFERT260625</t>
+        </is>
+      </c>
+      <c r="C192" s="5" t="inlineStr">
+        <is>
+          <t>Fertilizers &amp; Agrochemicals</t>
+        </is>
+      </c>
+      <c r="D192" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" s="6" t="n">
+        <v>513000</v>
+      </c>
+      <c r="Q192" s="7" t="n">
+        <v>2846.89</v>
+      </c>
+      <c r="R192" s="8" t="n">
+        <v>0.00100935</v>
+      </c>
+      <c r="S192" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T192" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U192" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V192" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W192" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X192" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y192" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z192" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA192" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB192" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC192" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD192" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE192" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF192" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG192" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH192" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI192" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ192" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>TREPS 02-Jun-2025 DEPO 10</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>INCBLO020625</t>
+        </is>
+      </c>
+      <c r="C193" s="5" t="inlineStr">
+        <is>
+          <t>N.A.</t>
+        </is>
+      </c>
+      <c r="D193" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" s="6" t="n">
+        <v>1827102.8</v>
+      </c>
+      <c r="Q193" s="7" t="n">
+        <v>182652.41</v>
+      </c>
+      <c r="R193" s="8" t="n">
+        <v>0.06475838</v>
+      </c>
+      <c r="S193" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V193" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W193" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y193" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z193" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB193" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC193" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE193" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF193" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG193" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH193" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI193" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ193" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="inlineStr">
+        <is>
+          <t>Larsen &amp; Toubro Limited 27/03/2025</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>LT270325</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" s="6" t="n">
+        <v>1071000</v>
+      </c>
+      <c r="H194" s="7" t="n">
+        <v>34073.87</v>
+      </c>
+      <c r="I194" s="8" t="n">
+        <v>0.01492346</v>
+      </c>
+      <c r="J194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W194" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z194" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC194" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF194" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG194" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH194" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI194" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ194" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>Oil and Natural Gas Corporation Ltd. 27/03/2025</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>ONGC270325</t>
+        </is>
+      </c>
+      <c r="C195" s="5" t="inlineStr">
+        <is>
+          <t>Oil</t>
+        </is>
+      </c>
+      <c r="D195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E195" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F195" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G195" s="6" t="n">
+        <v>8387225</v>
+      </c>
+      <c r="H195" s="7" t="n">
+        <v>19005.45</v>
+      </c>
+      <c r="I195" s="8" t="n">
+        <v>0.00832389</v>
+      </c>
+      <c r="J195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q195" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R195" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T195" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W195" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X195" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z195" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA195" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC195" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD195" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF195" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG195" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH195" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI195" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ195" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="inlineStr">
+        <is>
+          <t>GAIL (India) Limited 27/03/2025</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>GAIL270325</t>
+        </is>
+      </c>
+      <c r="C196" s="5" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="D196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" s="6" t="n">
+        <v>2968050</v>
+      </c>
+      <c r="H196" s="7" t="n">
+        <v>4646.48</v>
+      </c>
+      <c r="I196" s="8" t="n">
+        <v>0.00203504</v>
+      </c>
+      <c r="J196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q196" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R196" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T196" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W196" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X196" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z196" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA196" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC196" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD196" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF196" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG196" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH196" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI196" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ196" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>TREPS 03-Mar-2025 DEPO 10</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>INCBLO030325</t>
+        </is>
+      </c>
+      <c r="C197" s="5" t="inlineStr">
+        <is>
+          <t>N.A.</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G197" s="6" t="n">
+        <v>1840647.9</v>
+      </c>
+      <c r="H197" s="7" t="n">
+        <v>184001.66</v>
+      </c>
+      <c r="I197" s="8" t="n">
+        <v>0.08058788</v>
+      </c>
+      <c r="J197" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q197" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R197" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T197" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V197" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W197" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X197" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y197" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z197" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA197" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB197" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC197" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD197" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE197" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF197" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG197" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH197" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI197" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ197" s="8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="9" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="D191" s="10" t="n">
+      <c r="D198" s="10" t="n">
         <v>608884421.9</v>
       </c>
-      <c r="E191" s="11" t="n">
+      <c r="E198" s="11" t="n">
         <v>2567685.499999999</v>
       </c>
-      <c r="F191" s="12" t="n">
+      <c r="F198" s="12" t="n">
         <v>1.0198</v>
       </c>
-      <c r="G191" s="10" t="n">
+      <c r="G198" s="10" t="n">
         <v>603580914.9</v>
       </c>
-      <c r="H191" s="11" t="n">
+      <c r="H198" s="11" t="n">
         <v>2330474.89</v>
       </c>
-      <c r="I191" s="12" t="n">
+      <c r="I198" s="12" t="n">
         <v>1.02068667</v>
       </c>
-      <c r="J191" s="10" t="n">
+      <c r="J198" s="10" t="n">
         <v>641790117.1</v>
       </c>
-      <c r="K191" s="11" t="n">
+      <c r="K198" s="11" t="n">
         <v>2501109.800000002</v>
       </c>
-      <c r="L191" s="12" t="n">
+      <c r="L198" s="12" t="n">
         <v>1.00475961</v>
       </c>
-      <c r="M191" s="10" t="n">
+      <c r="M198" s="10" t="n">
         <v>692429148.6</v>
       </c>
-      <c r="N191" s="11" t="n">
+      <c r="N198" s="11" t="n">
         <v>2643625.08</v>
       </c>
-      <c r="O191" s="12" t="n">
+      <c r="O198" s="12" t="n">
         <v>1.00818887</v>
       </c>
-      <c r="P191" s="10" t="n">
+      <c r="P198" s="10" t="n">
         <v>731210939.8</v>
       </c>
-      <c r="Q191" s="11" t="n">
+      <c r="Q198" s="11" t="n">
         <v>2840004.41</v>
       </c>
-      <c r="R191" s="12" t="n">
+      <c r="R198" s="12" t="n">
         <v>1.006907529999999</v>
       </c>
-      <c r="S191" s="10" t="n">
+      <c r="S198" s="10" t="n">
         <v>769771505</v>
       </c>
-      <c r="T191" s="11" t="n">
+      <c r="T198" s="11" t="n">
         <v>2956059.75</v>
       </c>
-      <c r="U191" s="12" t="n">
+      <c r="U198" s="12" t="n">
         <v>0.9976883900000001</v>
       </c>
-      <c r="V191" s="10" t="n">
+      <c r="V198" s="10" t="n">
         <v>751591776</v>
       </c>
-      <c r="W191" s="11" t="n">
+      <c r="W198" s="11" t="n">
         <v>2879526.99</v>
       </c>
-      <c r="X191" s="12" t="n">
+      <c r="X198" s="12" t="n">
         <v>1.0012951</v>
       </c>
-      <c r="Y191" s="10" t="n">
+      <c r="Y198" s="10" t="n">
         <v>801253445.7</v>
       </c>
-      <c r="Z191" s="11" t="n">
+      <c r="Z198" s="11" t="n">
         <v>2976556.91</v>
       </c>
-      <c r="AA191" s="12" t="n">
+      <c r="AA198" s="12" t="n">
         <v>1.0163226</v>
       </c>
-      <c r="AB191" s="10" t="n">
+      <c r="AB198" s="10" t="n">
         <v>801367416.6</v>
       </c>
-      <c r="AC191" s="11" t="n">
+      <c r="AC198" s="11" t="n">
         <v>3055303.059999998</v>
       </c>
-      <c r="AD191" s="12" t="n">
+      <c r="AD198" s="12" t="n">
         <v>1.00159444</v>
       </c>
-      <c r="AE191" s="10" t="n">
+      <c r="AE198" s="10" t="n">
         <v>859738033.8</v>
       </c>
-      <c r="AF191" s="11" t="n">
+      <c r="AF198" s="11" t="n">
         <v>3108619.999999997</v>
       </c>
-      <c r="AG191" s="12" t="n">
+      <c r="AG198" s="12" t="n">
         <v>1.03037793</v>
+      </c>
+      <c r="AH198" s="10" t="n">
+        <v>867072590.2</v>
+      </c>
+      <c r="AI198" s="11" t="n">
+        <v>2982935.200000001</v>
+      </c>
+      <c r="AJ198" s="12" t="n">
+        <v>1.00150402</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A1:AJ1"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="Y2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
@@ -20846,6 +23373,7 @@
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="S2:U2"/>
+    <mergeCell ref="AH2:AJ2"/>
     <mergeCell ref="V2:X2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
